--- a/Metro Seat Tracker - Greeting Quips.xlsx
+++ b/Metro Seat Tracker - Greeting Quips.xlsx
@@ -12,7 +12,8 @@
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="5" width="45" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="6" width="45" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -28,15 +29,20 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t xml:space="preserve">Profile</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t xml:space="preserve">Quip 1</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t xml:space="preserve">Quip 2</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t xml:space="preserve">Quip 3</t>
         </is>
@@ -55,15 +61,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
           <t xml:space="preserve">Good morning, {name}! Ready to ride?</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t xml:space="preserve">Early bird catches the worm — let's sit in a new seat today, {name}.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t xml:space="preserve">Rise and ride, {name}!</t>
         </is>
@@ -82,15 +93,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t xml:space="preserve">Weekend morning, {name}! No rush today.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t xml:space="preserve">Lazy Saturday vibes, {name} — let's still find a good seat.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t xml:space="preserve">Up early on a day off, {name}? Let's ride.</t>
         </is>
@@ -109,15 +125,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t xml:space="preserve">Good late morning, {name}! Let's find a seat.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t xml:space="preserve">Almost noon, {name} — perfect time for a ride.</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t xml:space="preserve">Late start today, {name}? No worries, let's log a seat.</t>
         </is>
@@ -136,15 +157,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
           <t xml:space="preserve">Brunch o'clock, {name}? Let's find a seat first.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t xml:space="preserve">Weekend late morning, {name} — no alarm, no rush.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t xml:space="preserve">Slept in, {name}? Let's still catch a good seat.</t>
         </is>
@@ -163,15 +189,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Good afternoon, {name}! Where to?</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t xml:space="preserve">Midday ride, {name}? Let's log a seat.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t xml:space="preserve">Afternoon commute, {name} — let's make it count.</t>
         </is>
@@ -190,15 +221,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t xml:space="preserve">Weekend afternoon, {name}! Where's today's adventure?</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t xml:space="preserve">Out and about, {name}? Let's see what seat we get.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t xml:space="preserve">Sunny ride, {name} — perfect afternoon for the Metro.</t>
         </is>
@@ -217,15 +253,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t xml:space="preserve">Good evening, {name}! Heading home?</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t xml:space="preserve">Evening ride, {name} — let's see what seat we get.</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t xml:space="preserve">Rush hour, {name}. Ready when you are.</t>
         </is>
@@ -244,15 +285,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
           <t xml:space="preserve">Weekend evening, {name}! Out for the night?</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t xml:space="preserve">Date night ride, {name}?</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t xml:space="preserve">Evening plans, {name}? Let's log the seat.</t>
         </is>
@@ -271,15 +317,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
           <t xml:space="preserve">Still riding, {name}? Night owl mode.</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t xml:space="preserve">Late one tonight, {name} — let's log this ride.</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t xml:space="preserve">Night ride, {name}. Stay safe out there.</t>
         </is>
@@ -298,17 +349,150 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t xml:space="preserve">All</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t xml:space="preserve">Weekend night out, {name}? Let's ride.</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t xml:space="preserve">Late night Metro, {name} — stay safe.</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t xml:space="preserve">Night owl on a day off, {name}?</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Early Morning (5-9am)</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weekday</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kyle</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kyle, log today's seat before the coffee kicks in.</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rise and grind, Kyle — first one to a new seat wins.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Morning, Kyle. Let's make it two-for-two this week.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon (12-5pm)</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weekday</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abby</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abby, tell me you found a window seat today.</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Afternoon lull, Abby? Perfect time to rate a station.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Abby! Any new brutalist favorites today?</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evening (5-9pm)</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weekday</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophie</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophie, any new seats to report tonight?</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evening ride, Sophie — make it a good one.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sophie! Rush hour's better with a plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Night (9pm-5am)</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weekend</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caroline</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Late one, Caroline? Log it before you forget.</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Caroline, night rides hit different on the Metro.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Weekend night, Caroline — stay safe out there.</t>
         </is>
       </c>
     </row>
